--- a/templates/enterprise-monthly-energy_v1.xlsx
+++ b/templates/enterprise-monthly-energy_v1.xlsx
@@ -196,106 +196,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>模板说明</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>18 位代码；有代码时优先按代码匹配企业</t>
-      </text>
-    </comment>
-    <comment ref="B2" authorId="0" shapeId="0">
-      <text>
-        <t>与营业执照一致；无信用代码时按名称匹配</t>
-      </text>
-    </comment>
-    <comment ref="C2" authorId="0" shapeId="0">
-      <text>
-        <t>格式 YYYY-MM，例如 2025-03；每家企业每月一行</t>
-      </text>
-    </comment>
-    <comment ref="D2" authorId="0" shapeId="0">
-      <text>
-        <t>从公共电网购入、计入电费结算的电量；万千瓦时请 ×10000</t>
-      </text>
-    </comment>
-    <comment ref="E2" authorId="0" shapeId="0">
-      <text>
-        <t>通过绿电交易或绿证对应获取的可再生能源电量，排放因子计 0</t>
-      </text>
-    </comment>
-    <comment ref="F2" authorId="0" shapeId="0">
-      <text>
-        <t>非化石能源电力直接供应（直连）电量，排放因子计 0</t>
-      </text>
-    </comment>
-    <comment ref="G2" authorId="0" shapeId="0">
-      <text>
-        <t>厂内光伏发电并自用的电量</t>
-      </text>
-    </comment>
-    <comment ref="H2" authorId="0" shapeId="0">
-      <text>
-        <t>厂内光伏发电送入电网的电量</t>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
-      <text>
-        <t>标准立方米；万立方米请 ×10000</t>
-      </text>
-    </comment>
-    <comment ref="J2" authorId="0" shapeId="0">
-      <text>
-        <t>外购蒸汽、热水（化石能源热源）。蒸汽按吨填写的，请按热焓换算为 GJ 后填写</t>
-      </text>
-    </comment>
-    <comment ref="K2" authorId="0" shapeId="0">
-      <text>
-        <t>热源为生物质、地热等非化石能源的外购热力</t>
-      </text>
-    </comment>
-    <comment ref="L2" authorId="0" shapeId="0">
-      <text>
-        <t>按吨填写；升请按实际密度换算</t>
-      </text>
-    </comment>
-    <comment ref="M2" authorId="0" shapeId="0">
-      <text>
-        <t>按吨填写</t>
-      </text>
-    </comment>
-    <comment ref="N2" authorId="0" shapeId="0">
-      <text>
-        <t>按吨填写</t>
-      </text>
-    </comment>
-    <comment ref="O2" authorId="0" shapeId="0">
-      <text>
-        <t>秸秆、木屑、成型燃料等</t>
-      </text>
-    </comment>
-    <comment ref="P2" authorId="0" shapeId="0">
-      <text>
-        <t>按吨填写</t>
-      </text>
-    </comment>
-    <comment ref="Q2" authorId="0" shapeId="0">
-      <text>
-        <t>从下拉列表选择，用于标记数据质量</t>
-      </text>
-    </comment>
-    <comment ref="R2" authorId="0" shapeId="0">
-      <text>
-        <t>可选</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11200,6 +11100,5 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/templates/enterprise-monthly-energy_v1.xlsx
+++ b/templates/enterprise-monthly-energy_v1.xlsx
@@ -11095,8 +11095,8 @@
     <dataValidation sqref="P3:P502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请填写数值" error="请填写不小于 0 的数字，不要带单位" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="Q3:Q502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="请从下拉列表选择" error="取值：手工台账、系统导出、计量表实测、发票/结算单" type="list">
-      <formula1>"手工台账,系统导出,计量表实测,发票/结算单"</formula1>
+    <dataValidation sqref="Q3:Q502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="请从下拉列表选择" error="取值：公开报道、手工台账、系统导出、计量表实测、发票/结算单" type="list">
+      <formula1>"公开报道,手工台账,系统导出,计量表实测,发票/结算单"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
